--- a/Katalog_Mikro_Berintegritas.xlsx
+++ b/Katalog_Mikro_Berintegritas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\SOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20BEEA9-CAF4-41DA-9EB0-9180DAED9DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC9246E-1A74-4BEA-87ED-88FF90DA63E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="122">
   <si>
     <t>MIKRO BERINTEGRITAS | KATALOG KAMPANYE</t>
   </si>
@@ -531,6 +531,37 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1Kg8bEm36nzXaQLyrtj3sPzBecwRqCeNB/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Ketemu Salah Satu ini, Stop Dulu!</t>
+  </si>
+  <si>
+    <t>MB-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Ketemu satu tanda ini? Stop dulu.* 🚩
+Halo Sobat Mikro,
+pernah ketemu yang begini?
+1. Debitur nggak tahu usahanya sendiri
+2. Datang bareng "pendamping"
+3. Minta cair cepat
+4. Alamat usaha beda dengan berkas
+5. KTP pinjam punya saudara
+6. Foto usaha milik orang lain
+7. Ada "uang terima kasih"
+8. "Nanti angsurannya saya yang urus"
+9. "Aman kok, sudah biasa"
+Nggak perlu nunggu banyak.
+*Satu tanda = berhenti dan cek ulang.*
+Nomor berapa yang paling sering kamu temui? 👇
+Lihat. Tolak. Laporkan.
+</t>
+  </si>
+  <si>
+    <t>Portrait</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KNF6v3y4pBXnZTKNRMCN6UR6iPvZYEXK/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -690,7 +721,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -705,6 +736,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,6 +818,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -954,7 +1000,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="KatalogMateri" displayName="KatalogMateri" ref="A5:I20" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="KatalogMateri" displayName="KatalogMateri" ref="A5:I22" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No. " dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ID Konten" dataDxfId="9"/>
@@ -1165,524 +1211,557 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6" style="8" customWidth="1"/>
-    <col min="2" max="2" width="7.90234375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.90234375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="20.94921875" style="25" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.234375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="26" style="10" customWidth="1"/>
-    <col min="9" max="9" width="13" style="12" customWidth="1"/>
-    <col min="10" max="16384" width="8.76171875" style="12"/>
+    <col min="1" max="1" width="6" style="10" customWidth="1"/>
+    <col min="2" max="2" width="7.90234375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90234375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="20.94921875" style="27" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.234375" style="10" customWidth="1"/>
+    <col min="8" max="8" width="26" style="12" customWidth="1"/>
+    <col min="9" max="9" width="13" style="14" customWidth="1"/>
+    <col min="10" max="16384" width="8.76171875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1" ht="25.8">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:9" s="10" customFormat="1" ht="25.8">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-    </row>
-    <row r="2" spans="1:9" s="21" customFormat="1" ht="12.9">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+    </row>
+    <row r="2" spans="1:9" s="23" customFormat="1" ht="12.9">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-    </row>
-    <row r="3" spans="1:9" s="21" customFormat="1" ht="12.9">
-      <c r="A3" s="20" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" s="23" customFormat="1" ht="12.9">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="1:9" s="14" customFormat="1">
-      <c r="A5" s="9" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" s="16" customFormat="1">
+      <c r="A5" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="206.4">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="25" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="206.4">
-      <c r="A7" s="17">
+      <c r="A7" s="19">
         <v>2</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="26" t="s">
         <v>110</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="180.6">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>3</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="25" t="s">
         <v>111</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="193.5">
-      <c r="A9" s="17">
+      <c r="A9" s="19">
         <v>4</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="26" t="s">
         <v>99</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="193.5">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="25" t="s">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="180.6">
-      <c r="A11" s="17">
+      <c r="A11" s="19">
         <v>6</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="26" t="s">
         <v>101</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="154.80000000000001">
-      <c r="A12" s="17">
+      <c r="A12" s="19">
         <v>7</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="24" t="s">
+      <c r="C12" s="19"/>
+      <c r="D12" s="26" t="s">
         <v>115</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="34" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="167.7">
-      <c r="A13" s="15">
+      <c r="A13" s="17">
         <v>8</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="25" t="s">
         <v>102</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="387">
-      <c r="A14" s="17">
+      <c r="A14" s="19">
         <v>9</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="232.2">
-      <c r="A15" s="15">
+      <c r="A15" s="17">
         <v>10</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="25" t="s">
         <v>104</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="167.7">
-      <c r="A16" s="17">
+      <c r="A16" s="19">
         <v>11</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="26" t="s">
         <v>105</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="19" t="s">
         <v>54</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="141.9">
-      <c r="A17" s="15">
+      <c r="A17" s="17">
         <v>12</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="25" t="s">
         <v>106</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="15" t="s">
+      <c r="F17" s="18"/>
+      <c r="G17" s="17" t="s">
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="283.8">
-      <c r="A18" s="17">
+      <c r="A18" s="19">
         <v>13</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="26" t="s">
         <v>107</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="18"/>
-      <c r="G18" s="17" t="s">
+      <c r="F18" s="20"/>
+      <c r="G18" s="19" t="s">
         <v>54</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="154.80000000000001">
-      <c r="A19" s="15">
+      <c r="A19" s="17">
         <v>14</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="25" t="s">
         <v>108</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="15" t="s">
+      <c r="F19" s="18"/>
+      <c r="G19" s="17" t="s">
         <v>54</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I19" s="16" t="s">
+      <c r="I19" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="232.2">
-      <c r="A20" s="17">
+      <c r="A20" s="19">
         <v>15</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="26" t="s">
         <v>109</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="17" t="s">
+      <c r="F20" s="20"/>
+      <c r="G20" s="19" t="s">
         <v>54</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I20" s="16" t="s">
+      <c r="I20" s="18" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="21" spans="1:9" ht="331.2">
+      <c r="A21" s="36">
+        <v>16</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="D22" s="36"/>
+      <c r="I22" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1691,7 +1770,7 @@
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="C6:C2001" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="C6:C2001 B22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Gambar,Video"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="G6:G2001" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -1703,10 +1782,11 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H12" r:id="rId1" xr:uid="{F990574E-79AC-45A5-B7B1-346435E2746D}"/>
+    <hyperlink ref="H21" r:id="rId2" xr:uid="{805462C0-1AE2-4D67-898E-C299EC747BEE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1717,148 +1797,148 @@
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="15.6640625" style="5"/>
-    <col min="2" max="2" width="15.6640625" style="30"/>
+    <col min="2" max="2" width="15.6640625" style="32"/>
     <col min="3" max="6" width="15.6640625" style="5"/>
     <col min="7" max="7" width="30.90234375" style="5" customWidth="1"/>
     <col min="8" max="16384" width="15.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="30" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="31" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="30" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="31" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="30" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="31" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="30" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="31" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="30" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="31" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="30" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="31" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="30" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="31" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="23.2" customHeight="1">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="23.2" customHeight="1">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="31" t="s">
         <v>97</v>
       </c>
     </row>
